--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>具名覆写</t>
         </is>
       </c>
@@ -485,6 +490,11 @@
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>need</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>namedOverride</t>
         </is>
@@ -502,7 +512,6 @@
           <t>fox</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -516,7 +525,6 @@
           <t>crow</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -530,7 +538,6 @@
           <t>rabbit</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -544,7 +551,6 @@
           <t>hedgehog</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -558,7 +564,6 @@
           <t>rabbit</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -572,7 +577,6 @@
           <t>fox</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -586,7 +590,6 @@
           <t>crow</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -600,7 +603,6 @@
           <t>hedgehog</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -614,7 +616,6 @@
           <t>fox</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -512,6 +512,11 @@
           <t>fox</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Need_修理电路</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +530,11 @@
           <t>crow</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -538,6 +548,11 @@
           <t>rabbit</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Need_新需求</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -551,6 +566,11 @@
           <t>hedgehog</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -564,6 +584,11 @@
           <t>rabbit</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Need_修理电路</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -577,6 +602,11 @@
           <t>fox</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Need_新需求</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -590,6 +620,11 @@
           <t>crow</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -603,6 +638,11 @@
           <t>hedgehog</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Need_新需求</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -614,6 +654,11 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>fox</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Need_修理电路</t>
         </is>
       </c>
     </row>

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -1,54 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\2026MasterHouse\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796172F6-AEE4-4C46-9F7B-51F33ADABF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="345" yWindow="2040" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="日程" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="日程" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>出现时刻(分钟)</t>
+  </si>
+  <si>
+    <t>种族id</t>
+  </si>
+  <si>
+    <t>需求</t>
+  </si>
+  <si>
+    <t>具名覆写</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>appearMinute</t>
+  </si>
+  <si>
+    <t>race</t>
+  </si>
+  <si>
+    <t>need</t>
+  </si>
+  <si>
+    <t>namedOverride</t>
+  </si>
+  <si>
+    <t>rabbit</t>
+  </si>
+  <si>
+    <t>Need_修理电路</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>Need_要蓝色椅子</t>
+  </si>
+  <si>
+    <t>goat</t>
+  </si>
+  <si>
+    <t>Need_新需求</t>
+  </si>
+  <si>
+    <t>wolf</t>
+  </si>
+  <si>
+    <t>ox</t>
+  </si>
+  <si>
+    <t>leopard</t>
+  </si>
+  <si>
+    <t>cheetah</t>
+  </si>
+  <si>
+    <t>yak</t>
+  </si>
+  <si>
+    <t>Need_咖啡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
+        <fgColor rgb="FF4F81BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,86 +154,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -432,237 +462,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>出现时刻(分钟)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>种族id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>需求</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>具名覆写</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>appearMinute</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>need</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>namedOverride</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>510</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>fox</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Need_修理电路</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>550</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>crow</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>600</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>rabbit</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Need_新需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>840</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>hedgehog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>520</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>rabbit</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Need_修理电路</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>570</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>fox</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Need_新需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>780</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>crow</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>540</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>hedgehog</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Need_新需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>660</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>fox</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Need_修理电路</t>
-        </is>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>750</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796172F6-AEE4-4C46-9F7B-51F33ADABF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E193C-09A1-4F1E-8CD7-9B8DD1BDF40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="2040" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5295" yWindow="2475" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日程" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <t>yak</t>
   </si>
   <si>
-    <t>Need_咖啡</t>
+    <t>Need_制作咖啡</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -517,7 +517,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -545,7 +545,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\2026MasterHouse\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E193C-09A1-4F1E-8CD7-9B8DD1BDF40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F0B792-D737-4F5C-9B8E-764D878C9BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5295" yWindow="2475" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日程" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>Need_要蓝色椅子</t>
   </si>
   <si>
-    <t>goat</t>
-  </si>
-  <si>
     <t>Need_新需求</t>
   </si>
   <si>
@@ -86,6 +83,10 @@
   </si>
   <si>
     <t>Need_制作咖啡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need_要蓝色椅子</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -106,14 +107,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -514,10 +513,10 @@
         <v>510</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -528,7 +527,7 @@
         <v>550</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -542,7 +541,7 @@
         <v>600</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -556,10 +555,10 @@
         <v>840</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
@@ -570,7 +569,7 @@
         <v>520</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -584,10 +583,10 @@
         <v>570</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
@@ -598,7 +597,7 @@
         <v>780</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -612,10 +611,10 @@
         <v>540</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
@@ -626,7 +625,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F0B792-D737-4F5C-9B8E-764D878C9BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62A0FA8-28A5-4280-BED2-4EE0C6518B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1890" yWindow="720" windowWidth="16065" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日程" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>天</t>
   </si>
@@ -55,9 +55,6 @@
     <t>rabbit</t>
   </si>
   <si>
-    <t>Need_修理电路</t>
-  </si>
-  <si>
     <t>cat</t>
   </si>
   <si>
@@ -82,11 +79,11 @@
     <t>yak</t>
   </si>
   <si>
-    <t>Need_制作咖啡</t>
+    <t>Need_要蓝色椅子</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Need_要蓝色椅子</t>
+    <t>Need_电路教程</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -107,12 +104,16 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -513,7 +514,7 @@
         <v>510</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
@@ -527,10 +528,10 @@
         <v>550</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
@@ -541,10 +542,10 @@
         <v>600</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
@@ -555,10 +556,10 @@
         <v>840</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
@@ -572,7 +573,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
@@ -583,10 +584,10 @@
         <v>570</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
@@ -597,10 +598,10 @@
         <v>780</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
@@ -611,10 +612,10 @@
         <v>540</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
@@ -625,10 +626,10 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
@@ -639,10 +640,10 @@
         <v>750</v>
       </c>
       <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
         <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62A0FA8-28A5-4280-BED2-4EE0C6518B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4A8780-C897-49DA-BA68-09E237CAA6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="720" windowWidth="16065" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="990" yWindow="2340" windowWidth="21540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日程" sheetId="1" r:id="rId1"/>
@@ -528,7 +528,7 @@
         <v>550</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
@@ -542,7 +542,7 @@
         <v>600</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -1,131 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4A8780-C897-49DA-BA68-09E237CAA6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="2340" windowWidth="21540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="990" yWindow="2340" windowWidth="21540" windowHeight="13260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="日程" sheetId="1" r:id="rId1"/>
+    <sheet name="日程" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
-  <si>
-    <t>天</t>
-  </si>
-  <si>
-    <t>出现时刻(分钟)</t>
-  </si>
-  <si>
-    <t>种族id</t>
-  </si>
-  <si>
-    <t>需求</t>
-  </si>
-  <si>
-    <t>具名覆写</t>
-  </si>
-  <si>
-    <t>day</t>
-  </si>
-  <si>
-    <t>appearMinute</t>
-  </si>
-  <si>
-    <t>race</t>
-  </si>
-  <si>
-    <t>need</t>
-  </si>
-  <si>
-    <t>namedOverride</t>
-  </si>
-  <si>
-    <t>rabbit</t>
-  </si>
-  <si>
-    <t>cat</t>
-  </si>
-  <si>
-    <t>Need_要蓝色椅子</t>
-  </si>
-  <si>
-    <t>Need_新需求</t>
-  </si>
-  <si>
-    <t>wolf</t>
-  </si>
-  <si>
-    <t>ox</t>
-  </si>
-  <si>
-    <t>leopard</t>
-  </si>
-  <si>
-    <t>cheetah</t>
-  </si>
-  <si>
-    <t>yak</t>
-  </si>
-  <si>
-    <t>Need_要蓝色椅子</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Need_电路教程</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
-      <i/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -154,27 +79,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -462,193 +446,256 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>天</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>出现时刻(分钟)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>种族id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>具名覆写</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>appearMinute</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>need</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>namedOverride</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" t="n">
+        <v>510</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Need_修理电路_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>550</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>leopard</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cheetah</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Need_修理电路_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yak</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B7" t="n">
+        <v>520</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Need_修理电路_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="n">
+        <v>570</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wolf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Need_新需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>780</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ox</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>510</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>550</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>600</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>840</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>520</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>570</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>780</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10">
+      <c r="B10" t="n">
+        <v>540</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Need_新需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>3</v>
       </c>
-      <c r="B10">
-        <v>540</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11">
+      <c r="B11" t="n">
+        <v>660</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Need_修理电路_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B11">
-        <v>660</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>750</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Need_新需求</t>
+          <t>Need_修理电路_02</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Need_新需求</t>
+          <t>Need_修理电路_02</t>
         </is>
       </c>
     </row>

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -1,56 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F2160B-5CE1-4F79-8F35-9616DF76E365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="990" yWindow="2340" windowWidth="21540" windowHeight="13260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="5700" yWindow="915" windowWidth="21540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="日程" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="日程" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>出现时刻(分钟)</t>
+  </si>
+  <si>
+    <t>种族id</t>
+  </si>
+  <si>
+    <t>需求</t>
+  </si>
+  <si>
+    <t>具名覆写</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>appearMinute</t>
+  </si>
+  <si>
+    <t>race</t>
+  </si>
+  <si>
+    <t>need</t>
+  </si>
+  <si>
+    <t>namedOverride</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>Need_修理电路_01</t>
+  </si>
+  <si>
+    <t>leopard</t>
+  </si>
+  <si>
+    <t>Need_要蓝色椅子</t>
+  </si>
+  <si>
+    <t>cheetah</t>
+  </si>
+  <si>
+    <t>yak</t>
+  </si>
+  <si>
+    <t>ox</t>
+  </si>
+  <si>
+    <t>wolf</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">540	</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">600	</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">660	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">780	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">840	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">900	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">960	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1020	</t>
+  </si>
+  <si>
+    <t>Need_兔-化妆台</t>
+  </si>
+  <si>
+    <t>Need_兔-化妆台</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need_修理电路_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need_菜-节拍器</t>
+  </si>
+  <si>
+    <t>Need_制作咖啡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need_修理电路_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need_顿-收音机</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rabbit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <i val="1"/>
-      <color rgb="FF666666"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -78,87 +206,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -446,256 +524,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="16" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>出现时刻(分钟)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>种族id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>需求</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>具名覆写</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>appearMinute</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>need</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>namedOverride</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Need_修理电路_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B4" t="n">
-        <v>550</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>leopard</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B3" s="5">
+        <v>480</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B5" t="n">
-        <v>600</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>cheetah</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Need_修理电路_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B6" t="n">
-        <v>840</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>yak</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" t="n">
-        <v>520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>rabbit</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Need_修理电路_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" t="n">
-        <v>570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>wolf</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Need_修理电路_02</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" t="n">
-        <v>780</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ox</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" t="n">
-        <v>540</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Need_修理电路_02</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" t="n">
-        <v>660</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Need_修理电路_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12">
         <v>3</v>
       </c>
-      <c r="B12" t="n">
-        <v>750</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
+      <c r="B12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F2160B-5CE1-4F79-8F35-9616DF76E365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6469F09D-4ECE-46F0-90FF-9DDA0BFD36D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="915" windowWidth="21540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5685" yWindow="5190" windowWidth="21540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日程" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>天</t>
   </si>
@@ -77,35 +77,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">540	</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">600	</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">660	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">780	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">840	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">900	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">960	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1020	</t>
-  </si>
-  <si>
     <t>Need_兔-化妆台</t>
   </si>
   <si>
@@ -137,6 +108,14 @@
   </si>
   <si>
     <t>rabbit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">500	</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">560	</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +566,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -600,14 +579,14 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>19</v>
+      <c r="B5" s="5">
+        <v>530</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
@@ -615,97 +594,97 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>21</v>
+      <c r="B7" s="5">
+        <v>560</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
+      <c r="B8" s="5">
+        <v>580</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
+      <c r="B9" s="5">
+        <v>600</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>24</v>
+      <c r="B10" s="5">
+        <v>620</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>25</v>
+      <c r="B11" s="5">
+        <v>640</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>3</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="5">
+        <v>660</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -1,163 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6469F09D-4ECE-46F0-90FF-9DDA0BFD36D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="5190" windowWidth="21540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5685" yWindow="5190" windowWidth="21540" windowHeight="13260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="日程" sheetId="1" r:id="rId1"/>
+    <sheet name="日程" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
-  <si>
-    <t>天</t>
-  </si>
-  <si>
-    <t>出现时刻(分钟)</t>
-  </si>
-  <si>
-    <t>种族id</t>
-  </si>
-  <si>
-    <t>需求</t>
-  </si>
-  <si>
-    <t>具名覆写</t>
-  </si>
-  <si>
-    <t>day</t>
-  </si>
-  <si>
-    <t>appearMinute</t>
-  </si>
-  <si>
-    <t>race</t>
-  </si>
-  <si>
-    <t>need</t>
-  </si>
-  <si>
-    <t>namedOverride</t>
-  </si>
-  <si>
-    <t>cat</t>
-  </si>
-  <si>
-    <t>Need_修理电路_01</t>
-  </si>
-  <si>
-    <t>leopard</t>
-  </si>
-  <si>
-    <t>Need_要蓝色椅子</t>
-  </si>
-  <si>
-    <t>cheetah</t>
-  </si>
-  <si>
-    <t>yak</t>
-  </si>
-  <si>
-    <t>ox</t>
-  </si>
-  <si>
-    <t>wolf</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Need_兔-化妆台</t>
-  </si>
-  <si>
-    <t>Need_兔-化妆台</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Need_修理电路_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Need_菜-节拍器</t>
-  </si>
-  <si>
-    <t>Need_制作咖啡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Need_修理电路_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Need_顿-收音机</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>yak</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rabbit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">500	</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">560	</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
-      <i/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -186,36 +79,95 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -503,193 +455,260 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="16" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" style="5" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>天</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>出现时刻(分钟)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>种族id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>具名覆写</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>appearMinute</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>need</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>namedOverride</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Need_修理电路_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500	</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>leopard</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>530</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cheetah</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Need_修理电路_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">560	</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yak</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Need_制作咖啡</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B7" s="5" t="n">
+        <v>560</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Need_兔-化妆台</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>580</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wolf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Need_修理电路_03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ox</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Need_顿-收音机</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5">
-        <v>480</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5">
-        <v>530</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" s="5">
-        <v>560</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5">
-        <v>580</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" s="5">
-        <v>600</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10">
+      <c r="B10" s="5" t="n">
+        <v>620</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Need_制作咖啡</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="5">
-        <v>620</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11">
+      <c r="B11" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>yak</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Need_莱-节拍器</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="5">
-        <v>640</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12" s="5">
+      <c r="B12" s="5" t="n">
         <v>660</v>
       </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Need_兔-化妆台</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Excel/访客日程表.xlsx
+++ b/Excel/访客日程表.xlsx
@@ -1,56 +1,147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE86CF30-1914-4D41-BE1A-5DF89D677A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5685" yWindow="5190" windowWidth="21540" windowHeight="13260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="720" yWindow="450" windowWidth="21540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="日程" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="日程" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>出现时刻(分钟)</t>
+  </si>
+  <si>
+    <t>种族id</t>
+  </si>
+  <si>
+    <t>需求</t>
+  </si>
+  <si>
+    <t>具名覆写</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>appearMinute</t>
+  </si>
+  <si>
+    <t>race</t>
+  </si>
+  <si>
+    <t>need</t>
+  </si>
+  <si>
+    <t>namedOverride</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>Need_修理电路_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500	</t>
+  </si>
+  <si>
+    <t>leopard</t>
+  </si>
+  <si>
+    <t>Need_要蓝色椅子</t>
+  </si>
+  <si>
+    <t>cheetah</t>
+  </si>
+  <si>
+    <t>Need_修理电路_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">560	</t>
+  </si>
+  <si>
+    <t>yak</t>
+  </si>
+  <si>
+    <t>Need_制作咖啡</t>
+  </si>
+  <si>
+    <t>rabbit</t>
+  </si>
+  <si>
+    <t>Need_兔-化妆台</t>
+  </si>
+  <si>
+    <t>wolf</t>
+  </si>
+  <si>
+    <t>Need_修理电路_03</t>
+  </si>
+  <si>
+    <t>ox</t>
+  </si>
+  <si>
+    <t>Need_顿-收音机</t>
+  </si>
+  <si>
+    <t>Need_莱-节拍器</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <i val="1"/>
-      <color rgb="FF666666"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -79,95 +170,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -455,260 +487,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" style="5" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="16" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>出现时刻(分钟)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>种族id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>需求</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>具名覆写</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>appearMinute</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>race</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>need</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>namedOverride</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
         <v>480</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Need_修理电路_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500	</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>leopard</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Need_要蓝色椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="5">
         <v>530</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>cheetah</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Need_修理电路_02</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">560	</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>yak</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Need_制作咖啡</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="5">
         <v>560</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>rabbit</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Need_兔-化妆台</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="5">
         <v>580</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>wolf</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Need_修理电路_03</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="5">
         <v>600</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ox</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Need_顿-收音机</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="5">
         <v>620</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Need_制作咖啡</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="5">
         <v>640</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yak</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Need_莱-节拍器</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12">
         <v>3</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="5">
         <v>660</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>rabbit</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Need_兔-化妆台</t>
-        </is>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>